--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dibendu/Documents/atp_analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dibendu/Documents/GitHub/Fit_repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CCF11E-4663-2844-9218-D2FD0190E36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E015C3-F49B-BC40-B804-B456E334D36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="760" windowWidth="29900" windowHeight="21480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -298,176 +298,80 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>0.2</v>
-      </c>
-      <c r="C3">
-        <v>1.06</v>
-      </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>0.6</v>
-      </c>
-      <c r="C4">
-        <v>1.8125</v>
-      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1.8794643</v>
-      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>1.5</v>
-      </c>
-      <c r="C6">
-        <v>2.0580357</v>
-      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2.0803571000000001</v>
-      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>2.5</v>
-      </c>
-      <c r="C8">
-        <v>2.0357143</v>
-      </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>2.1696428999999999</v>
-      </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10">
-        <v>2.2366071000000001</v>
-      </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>5</v>
       </c>
-      <c r="B12">
-        <v>0.2</v>
-      </c>
-      <c r="C12">
-        <v>0.58035714285714335</v>
-      </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13">
-        <v>0.6</v>
-      </c>
-      <c r="C13">
-        <v>0.82589285714285787</v>
-      </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>5</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1.1160714285714284</v>
-      </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>5</v>
       </c>
-      <c r="B15">
-        <v>1.5</v>
-      </c>
-      <c r="C15">
-        <v>1.3169642857142869</v>
-      </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>5</v>
       </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>1.2276785714285714</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
         <v>5</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17">
-        <v>1.22</v>
       </c>
     </row>
   </sheetData>
